--- a/data/catalogo_maestro.xlsx
+++ b/data/catalogo_maestro.xlsx
@@ -8,21 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\taully_demand_forecast\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9B063D5-FBF3-4ADC-8D5A-659995EF332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C144A15-F34E-453E-95E4-B143DB63EA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="3165" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3135" yWindow="3090" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
     <sheet name="FUENTES" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="385">
   <si>
     <t>PRODUCTO</t>
   </si>
@@ -1174,13 +1173,16 @@
   </si>
   <si>
     <t xml:space="preserve">CIELO </t>
+  </si>
+  <si>
+    <t>Galletas OREO Original Paquete 12un</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1189,6 +1191,10 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1305,7 +1311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1379,10 +1385,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1401,7 +1412,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Catalogo200" displayName="Catalogo200" ref="A1:E202" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Catalogo200" displayName="Catalogo200" ref="A1:E203" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FAMILIA"/>
@@ -1621,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -2192,77 +2203,77 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>59</v>
+    <row r="34" spans="1:5" s="33" customFormat="1">
+      <c r="A34" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="32">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="13">
+      <c r="C35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="13">
         <v>8.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="28.5">
-      <c r="A35" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="15">
-        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.5">
       <c r="A36" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E36" s="15">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.5">
       <c r="A37" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E37" s="15">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="28.5">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>66</v>
@@ -2271,18 +2282,18 @@
         <v>61</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E38" s="15">
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="28.5">
       <c r="A39" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>61</v>
@@ -2291,12 +2302,12 @@
         <v>62</v>
       </c>
       <c r="E39" s="15">
-        <v>9.6999999999999993</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>69</v>
@@ -2313,7 +2324,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>69</v>
@@ -2328,12 +2339,12 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.5">
+    <row r="42" spans="1:5">
       <c r="A42" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>61</v>
@@ -2342,46 +2353,46 @@
         <v>62</v>
       </c>
       <c r="E42" s="15">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28.5">
+      <c r="A43" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="15">
         <v>13.9</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="28.5">
-      <c r="A43" s="16" t="s">
+    <row r="44" spans="1:5" ht="28.5">
+      <c r="A44" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="17">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E44" s="17">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>78</v>
@@ -2393,12 +2404,12 @@
         <v>78</v>
       </c>
       <c r="E45" s="17">
-        <v>4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>78</v>
@@ -2410,46 +2421,46 @@
         <v>78</v>
       </c>
       <c r="E46" s="17">
-        <v>11.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E47" s="17">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E48" s="17">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>84</v>
@@ -2461,131 +2472,131 @@
         <v>84</v>
       </c>
       <c r="E49" s="17">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E50" s="17">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E51" s="17">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E52" s="17">
-        <v>17.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E53" s="17">
-        <v>4.5999999999999996</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="17">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E54" s="17">
+      <c r="C55" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E55" s="17">
         <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="19">
-        <v>5.3</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E56" s="19">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>100</v>
@@ -2597,12 +2608,12 @@
         <v>100</v>
       </c>
       <c r="E57" s="19">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>100</v>
@@ -2614,29 +2625,29 @@
         <v>100</v>
       </c>
       <c r="E58" s="19">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E59" s="19">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>104</v>
@@ -2653,7 +2664,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>104</v>
@@ -2665,12 +2676,12 @@
         <v>104</v>
       </c>
       <c r="E61" s="19">
-        <v>10.199999999999999</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>104</v>
@@ -2682,15 +2693,15 @@
         <v>104</v>
       </c>
       <c r="E62" s="19">
-        <v>6.2</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>98</v>
@@ -2699,29 +2710,29 @@
         <v>104</v>
       </c>
       <c r="E63" s="19">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E64" s="19">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>111</v>
@@ -2733,12 +2744,12 @@
         <v>111</v>
       </c>
       <c r="E65" s="19">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>111</v>
@@ -2750,97 +2761,97 @@
         <v>111</v>
       </c>
       <c r="E66" s="19">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E67" s="19">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E68" s="19">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E69" s="19">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D70" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E70" s="19">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E70" s="19">
+      <c r="C71" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" s="19">
         <v>4.3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" s="13">
-        <v>3.3</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>49</v>
@@ -2852,66 +2863,66 @@
         <v>49</v>
       </c>
       <c r="E72" s="13">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="E73" s="13">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E74" s="13">
-        <v>4.0999999999999996</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="E75" s="13">
-        <v>3</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>29</v>
@@ -2920,15 +2931,15 @@
         <v>49</v>
       </c>
       <c r="E76" s="13">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="28.5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>29</v>
@@ -2937,15 +2948,15 @@
         <v>49</v>
       </c>
       <c r="E77" s="13">
-        <v>5.3</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="28.5">
       <c r="A78" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>29</v>
@@ -2957,12 +2968,12 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" ht="28.5">
       <c r="A79" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>29</v>
@@ -2971,32 +2982,32 @@
         <v>49</v>
       </c>
       <c r="E79" s="13">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="E80" s="13">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="28.5">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>29</v>
@@ -3005,267 +3016,267 @@
         <v>139</v>
       </c>
       <c r="E81" s="13">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="28.5">
       <c r="A82" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E82" s="13">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E83" s="13">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D84" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E84" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E84" s="13">
+      <c r="C85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E85" s="13">
         <v>2.1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E85" s="19">
-        <v>4.8</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E86" s="19">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E87" s="19">
-        <v>3.99</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E88" s="19">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="E88" s="19">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="28.5">
-      <c r="A89" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E89" s="19">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="28.5">
+      <c r="A90" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="E89" s="19">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="E90" s="19">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E91" s="19">
-        <v>12</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="E92" s="19">
-        <v>7.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="E93" s="19">
-        <v>10.49</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="E94" s="19">
-        <v>8.9</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D95" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E95" s="19">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E95" s="19">
+      <c r="C96" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E96" s="19">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E96" s="11">
-        <v>2.4</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>165</v>
@@ -3277,12 +3288,12 @@
         <v>165</v>
       </c>
       <c r="E97" s="11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>165</v>
@@ -3294,12 +3305,12 @@
         <v>165</v>
       </c>
       <c r="E98" s="11">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>165</v>
@@ -3311,12 +3322,12 @@
         <v>165</v>
       </c>
       <c r="E99" s="11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>165</v>
@@ -3328,63 +3339,63 @@
         <v>165</v>
       </c>
       <c r="E100" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E101" s="11">
         <v>11.9</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="16" t="s">
+    <row r="102" spans="1:5">
+      <c r="A102" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B102" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E101" s="17">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="28.5">
-      <c r="A102" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D102" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E102" s="17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="28.5">
+      <c r="A103" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E102" s="17">
+      <c r="C103" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E103" s="17">
         <v>50.9</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.5">
-      <c r="A103" s="10" t="s">
+    <row r="104" spans="1:5" ht="28.5">
+      <c r="A104" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E103" s="11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>6</v>
@@ -3396,46 +3407,46 @@
         <v>6</v>
       </c>
       <c r="E104" s="11">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E105" s="11">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E105" s="11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="28.5">
-      <c r="A106" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E106" s="11">
-        <v>12.2</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="28.5">
       <c r="A107" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>6</v>
@@ -3452,7 +3463,7 @@
     </row>
     <row r="108" spans="1:5" ht="28.5">
       <c r="A108" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>6</v>
@@ -3464,114 +3475,114 @@
         <v>6</v>
       </c>
       <c r="E108" s="11">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="28.5">
       <c r="A109" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E109" s="11">
-        <v>7.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E110" s="11">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E111" s="11">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E111" s="11">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="28.5">
-      <c r="A112" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="11">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="28.5">
+      <c r="A113" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="E112" s="11">
-        <v>30.9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E113" s="11">
-        <v>12.2</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E114" s="11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="28.5">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>6</v>
@@ -3583,12 +3594,12 @@
         <v>6</v>
       </c>
       <c r="E115" s="11">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="28.5">
       <c r="A116" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>6</v>
@@ -3600,182 +3611,182 @@
         <v>6</v>
       </c>
       <c r="E116" s="11">
-        <v>25.4</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="E117" s="11">
-        <v>2.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E118" s="11">
-        <v>10.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="E119" s="11">
-        <v>18</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E120" s="11">
-        <v>8.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E121" s="11">
-        <v>13.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
       <c r="E122" s="11">
-        <v>6.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E123" s="11">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="E124" s="11">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="E125" s="11">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="E126" s="11">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>6</v>
@@ -3792,228 +3803,228 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="E128" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D129" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E129" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="E129" s="11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="28.5">
-      <c r="A130" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="E130" s="11">
-        <v>20.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="28.5">
       <c r="A131" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="E131" s="11">
-        <v>12.9</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="28.5">
       <c r="A132" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E132" s="11">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="28.5">
+      <c r="A133" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E132" s="11">
+      <c r="C133" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E133" s="11">
         <v>10.9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="28.5">
-      <c r="A133" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E133" s="13">
-        <v>12.9</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="28.5">
       <c r="A134" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E134" s="13">
-        <v>12</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="28.5">
       <c r="A135" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E135" s="13">
-        <v>4.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="28.5">
       <c r="A136" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D136" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E136" s="13">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="28.5">
+      <c r="A137" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="E136" s="13">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="E137" s="13">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>217</v>
+        <v>28</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>217</v>
+        <v>28</v>
       </c>
       <c r="E138" s="13">
-        <v>6.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E139" s="13">
-        <v>14.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="E140" s="13">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="28.5">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>28</v>
@@ -4025,80 +4036,80 @@
         <v>28</v>
       </c>
       <c r="E141" s="13">
-        <v>11.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="28.5">
       <c r="A142" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="E142" s="13">
         <v>11.5</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" ht="28.5">
       <c r="A143" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E143" s="13">
-        <v>5.0999999999999996</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E144" s="13">
-        <v>2</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E145" s="13">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="28.5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>228</v>
@@ -4110,131 +4121,131 @@
         <v>228</v>
       </c>
       <c r="E146" s="13">
-        <v>27.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="28.5">
       <c r="A147" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>43</v>
+        <v>228</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D147" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E147" s="13">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="28.5">
+      <c r="A148" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E147" s="13">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D148" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E148" s="13">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="E148" s="13">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="28.5">
-      <c r="A149" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D149" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E149" s="13">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="28.5">
+      <c r="A150" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="E149" s="13">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E150" s="13">
-        <v>25.9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D151" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E151" s="13">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="E151" s="13">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="28.5">
-      <c r="A152" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D152" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E152" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="28.5">
+      <c r="A153" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E152" s="13">
+      <c r="C153" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E153" s="13">
         <v>11.5</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="28.5">
-      <c r="A153" s="14" t="s">
+    <row r="154" spans="1:5" ht="28.5">
+      <c r="A154" s="14" t="s">
         <v>239</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E153" s="15">
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="14" t="s">
-        <v>240</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>69</v>
@@ -4246,12 +4257,12 @@
         <v>62</v>
       </c>
       <c r="E154" s="15">
-        <v>16.7</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>69</v>
@@ -4266,9 +4277,9 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="28.5">
+    <row r="156" spans="1:5">
       <c r="A156" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>69</v>
@@ -4285,10 +4296,10 @@
     </row>
     <row r="157" spans="1:5" ht="28.5">
       <c r="A157" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>61</v>
@@ -4297,15 +4308,15 @@
         <v>62</v>
       </c>
       <c r="E157" s="15">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="28.5">
       <c r="A158" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>61</v>
@@ -4314,15 +4325,15 @@
         <v>62</v>
       </c>
       <c r="E158" s="15">
-        <v>17.899999999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="28.5">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
       <c r="A159" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>61</v>
@@ -4331,15 +4342,15 @@
         <v>62</v>
       </c>
       <c r="E159" s="15">
-        <v>34.9</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="28.5">
       <c r="A160" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>28</v>
+        <v>247</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>61</v>
@@ -4348,49 +4359,49 @@
         <v>62</v>
       </c>
       <c r="E160" s="15">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="28.5">
       <c r="A161" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>250</v>
+        <v>28</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>250</v>
+        <v>62</v>
       </c>
       <c r="E161" s="15">
-        <v>24.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>69</v>
+        <v>250</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="E162" s="15">
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="28.5">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>61</v>
@@ -4399,15 +4410,15 @@
         <v>62</v>
       </c>
       <c r="E163" s="15">
-        <v>24.9</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="28.5">
       <c r="A164" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>61</v>
@@ -4416,49 +4427,49 @@
         <v>62</v>
       </c>
       <c r="E164" s="15">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="28.5">
       <c r="A165" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="E165" s="15">
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="28.5">
+    <row r="166" spans="1:5">
       <c r="A166" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>69</v>
+        <v>256</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>62</v>
+        <v>256</v>
       </c>
       <c r="E166" s="15">
-        <v>16.5</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="28.5">
       <c r="A167" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>61</v>
@@ -4467,12 +4478,12 @@
         <v>62</v>
       </c>
       <c r="E167" s="15">
-        <v>24.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="28.5">
       <c r="A168" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>66</v>
@@ -4484,15 +4495,15 @@
         <v>62</v>
       </c>
       <c r="E168" s="15">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="28.5">
       <c r="A169" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>61</v>
@@ -4501,49 +4512,49 @@
         <v>62</v>
       </c>
       <c r="E169" s="15">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="28.5">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D170" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E170" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="28.5">
+      <c r="A171" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B171" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="E170" s="15">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="E171" s="15">
-        <v>2.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>61</v>
@@ -4552,182 +4563,182 @@
         <v>62</v>
       </c>
       <c r="E172" s="15">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E173" s="15">
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="16" t="s">
+    <row r="174" spans="1:5">
+      <c r="A174" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="B174" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E173" s="17">
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" ht="28.5">
-      <c r="A174" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>267</v>
+        <v>91</v>
       </c>
       <c r="E174" s="17">
-        <v>13.5</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="28.5">
       <c r="A175" s="16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="E175" s="17">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="28.5">
       <c r="A176" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D176" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E176" s="17">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="28.5">
+      <c r="A177" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="E176" s="17">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C177" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D177" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E177" s="17">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="E177" s="17">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="28.5">
-      <c r="A178" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D178" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E178" s="17">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="28.5">
+      <c r="A179" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="E178" s="17">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D179" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E179" s="17">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B180" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="E179" s="17">
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="28.5">
-      <c r="A180" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D180" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E180" s="17">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="28.5">
+      <c r="A181" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="E180" s="17">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E181" s="17">
-        <v>16.899999999999999</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E182" s="17">
-        <v>28.1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="28.5">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>84</v>
@@ -4739,63 +4750,63 @@
         <v>84</v>
       </c>
       <c r="E183" s="17">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="28.5">
       <c r="A184" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E184" s="17">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E185" s="17">
-        <v>28.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>267</v>
+        <v>84</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>267</v>
+        <v>84</v>
       </c>
       <c r="E186" s="17">
-        <v>4.9000000000000004</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>267</v>
@@ -4807,63 +4818,63 @@
         <v>267</v>
       </c>
       <c r="E187" s="17">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E188" s="17">
         <v>20.9</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="28.5">
-      <c r="A188" s="18" t="s">
+    <row r="189" spans="1:5" ht="28.5">
+      <c r="A189" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B189" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="C188" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="E188" s="19">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>152</v>
+        <v>282</v>
       </c>
       <c r="E189" s="19">
-        <v>20.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="E190" s="19">
-        <v>22.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>111</v>
@@ -4875,46 +4886,46 @@
         <v>111</v>
       </c>
       <c r="E191" s="19">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="E192" s="19">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E193" s="19">
-        <v>20.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>148</v>
@@ -4926,29 +4937,29 @@
         <v>148</v>
       </c>
       <c r="E194" s="19">
-        <v>17.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E195" s="19">
-        <v>40.9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>152</v>
@@ -4960,29 +4971,29 @@
         <v>152</v>
       </c>
       <c r="E196" s="19">
-        <v>4.49</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="E197" s="19">
-        <v>21.9</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>282</v>
@@ -4994,29 +5005,29 @@
         <v>282</v>
       </c>
       <c r="E198" s="19">
-        <v>42</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E199" s="19">
-        <v>4.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>294</v>
@@ -5028,12 +5039,12 @@
         <v>294</v>
       </c>
       <c r="E200" s="19">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>294</v>
@@ -5045,27 +5056,45 @@
         <v>294</v>
       </c>
       <c r="E201" s="19">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E202" s="19">
         <v>3.2</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
-      <c r="A202" s="20" t="s">
+    <row r="203" spans="1:5">
+      <c r="A203" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="B202" s="21" t="s">
+      <c r="B203" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C202" s="21" t="s">
+      <c r="C203" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="D202" s="21" t="s">
+      <c r="D203" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="E202" s="22">
+      <c r="E203" s="22">
         <v>4.5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/catalogo_maestro.xlsx
+++ b/data/catalogo_maestro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\taully_demand_forecast\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C144A15-F34E-453E-95E4-B143DB63EA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945FFBCF-BD61-41D1-BB45-04F62984445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3135" yWindow="3090" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="387">
   <si>
     <t>PRODUCTO</t>
   </si>
@@ -1176,6 +1176,12 @@
   </si>
   <si>
     <t>Galletas OREO Original Paquete 12un</t>
+  </si>
+  <si>
+    <t>Galleta Morochas Clásicas 30 gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLOSINAS </t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1389,11 +1395,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1412,7 +1421,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Catalogo200" displayName="Catalogo200" ref="A1:E203" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Catalogo200" displayName="Catalogo200" ref="A1:E204" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PRODUCTO"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FAMILIA"/>
@@ -1632,7 +1641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -2221,76 +2230,76 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="D35" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="32">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E36" s="13">
         <v>8.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="28.5">
-      <c r="A36" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="15">
-        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="28.5">
       <c r="A37" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E37" s="15">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28.5">
       <c r="A38" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E38" s="15">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="28.5">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>66</v>
@@ -2299,18 +2308,18 @@
         <v>61</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E39" s="15">
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="28.5">
       <c r="A40" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>61</v>
@@ -2319,12 +2328,12 @@
         <v>62</v>
       </c>
       <c r="E40" s="15">
-        <v>9.6999999999999993</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>69</v>
@@ -2341,7 +2350,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>69</v>
@@ -2356,12 +2365,12 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="28.5">
+    <row r="43" spans="1:5">
       <c r="A43" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>61</v>
@@ -2370,46 +2379,46 @@
         <v>62</v>
       </c>
       <c r="E43" s="15">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="28.5">
+      <c r="A44" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="15">
         <v>13.9</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.5">
-      <c r="A44" s="16" t="s">
+    <row r="45" spans="1:5" ht="28.5">
+      <c r="A45" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44" s="17">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E45" s="17">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>78</v>
@@ -2421,12 +2430,12 @@
         <v>78</v>
       </c>
       <c r="E46" s="17">
-        <v>4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>78</v>
@@ -2438,46 +2447,46 @@
         <v>78</v>
       </c>
       <c r="E47" s="17">
-        <v>11.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E48" s="17">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E49" s="17">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>84</v>
@@ -2489,131 +2498,131 @@
         <v>84</v>
       </c>
       <c r="E50" s="17">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E51" s="17">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E52" s="17">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E53" s="17">
-        <v>17.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E54" s="17">
-        <v>4.5999999999999996</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" s="17">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E55" s="17">
+      <c r="C56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="17">
         <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="19">
-        <v>5.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E57" s="19">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>100</v>
@@ -2625,12 +2634,12 @@
         <v>100</v>
       </c>
       <c r="E58" s="19">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>100</v>
@@ -2642,29 +2651,29 @@
         <v>100</v>
       </c>
       <c r="E59" s="19">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E60" s="19">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>104</v>
@@ -2681,7 +2690,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>104</v>
@@ -2693,12 +2702,12 @@
         <v>104</v>
       </c>
       <c r="E62" s="19">
-        <v>10.199999999999999</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>104</v>
@@ -2710,15 +2719,15 @@
         <v>104</v>
       </c>
       <c r="E63" s="19">
-        <v>6.2</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>98</v>
@@ -2727,29 +2736,29 @@
         <v>104</v>
       </c>
       <c r="E64" s="19">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E65" s="19">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>111</v>
@@ -2761,12 +2770,12 @@
         <v>111</v>
       </c>
       <c r="E66" s="19">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>111</v>
@@ -2778,97 +2787,97 @@
         <v>111</v>
       </c>
       <c r="E67" s="19">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E68" s="19">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E69" s="19">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E70" s="19">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D71" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E71" s="19">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E71" s="19">
+      <c r="C72" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="19">
         <v>4.3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" s="13">
-        <v>3.3</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>49</v>
@@ -2880,66 +2889,66 @@
         <v>49</v>
       </c>
       <c r="E73" s="13">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="E74" s="13">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E75" s="13">
-        <v>4.0999999999999996</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="E76" s="13">
-        <v>3</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>29</v>
@@ -2948,15 +2957,15 @@
         <v>49</v>
       </c>
       <c r="E77" s="13">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="28.5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>29</v>
@@ -2965,15 +2974,15 @@
         <v>49</v>
       </c>
       <c r="E78" s="13">
-        <v>5.3</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="28.5">
       <c r="A79" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>29</v>
@@ -2985,12 +2994,12 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" ht="28.5">
       <c r="A80" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>29</v>
@@ -2999,32 +3008,32 @@
         <v>49</v>
       </c>
       <c r="E80" s="13">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="E81" s="13">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="28.5">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>29</v>
@@ -3033,267 +3042,267 @@
         <v>139</v>
       </c>
       <c r="E82" s="13">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="28.5">
       <c r="A83" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E83" s="13">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E84" s="13">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D85" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E85" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E85" s="13">
+      <c r="C86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E86" s="13">
         <v>2.1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E86" s="19">
-        <v>4.8</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E87" s="19">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E88" s="19">
-        <v>3.99</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" s="19">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="E89" s="19">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="28.5">
-      <c r="A90" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E90" s="19">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="28.5">
+      <c r="A91" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="E90" s="19">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="E91" s="19">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E92" s="19">
-        <v>12</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="E93" s="19">
-        <v>7.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="E94" s="19">
-        <v>10.49</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="E95" s="19">
-        <v>8.9</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D96" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E96" s="19">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E96" s="19">
+      <c r="C97" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E97" s="19">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E97" s="11">
-        <v>2.4</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>165</v>
@@ -3305,12 +3314,12 @@
         <v>165</v>
       </c>
       <c r="E98" s="11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>165</v>
@@ -3322,12 +3331,12 @@
         <v>165</v>
       </c>
       <c r="E99" s="11">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>165</v>
@@ -3339,12 +3348,12 @@
         <v>165</v>
       </c>
       <c r="E100" s="11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>165</v>
@@ -3356,63 +3365,63 @@
         <v>165</v>
       </c>
       <c r="E101" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E102" s="11">
         <v>11.9</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="16" t="s">
+    <row r="103" spans="1:5">
+      <c r="A103" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B103" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E102" s="17">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="28.5">
-      <c r="A103" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D103" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E103" s="17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="28.5">
+      <c r="A104" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E103" s="17">
+      <c r="C104" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E104" s="17">
         <v>50.9</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="28.5">
-      <c r="A104" s="10" t="s">
+    <row r="105" spans="1:5" ht="28.5">
+      <c r="A105" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E104" s="11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>6</v>
@@ -3424,46 +3433,46 @@
         <v>6</v>
       </c>
       <c r="E105" s="11">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E106" s="11">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E106" s="11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="28.5">
-      <c r="A107" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E107" s="11">
-        <v>12.2</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="28.5">
       <c r="A108" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>6</v>
@@ -3480,7 +3489,7 @@
     </row>
     <row r="109" spans="1:5" ht="28.5">
       <c r="A109" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>6</v>
@@ -3492,114 +3501,114 @@
         <v>6</v>
       </c>
       <c r="E109" s="11">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="28.5">
       <c r="A110" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E110" s="11">
-        <v>7.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E111" s="11">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E112" s="11">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E112" s="11">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="28.5">
-      <c r="A113" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="11">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="28.5">
+      <c r="A114" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="E113" s="11">
-        <v>30.9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E114" s="11">
-        <v>12.2</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E115" s="11">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="28.5">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>6</v>
@@ -3611,12 +3620,12 @@
         <v>6</v>
       </c>
       <c r="E116" s="11">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="28.5">
       <c r="A117" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>6</v>
@@ -3628,182 +3637,182 @@
         <v>6</v>
       </c>
       <c r="E117" s="11">
-        <v>25.4</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="E118" s="11">
-        <v>2.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E119" s="11">
-        <v>10.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="E120" s="11">
-        <v>18</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E121" s="11">
-        <v>8.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E122" s="11">
-        <v>13.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
       <c r="E123" s="11">
-        <v>6.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E124" s="11">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="E125" s="11">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="E126" s="11">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="E127" s="11">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>6</v>
@@ -3820,228 +3829,228 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="E129" s="11">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D130" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E130" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="E130" s="11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="28.5">
-      <c r="A131" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>165</v>
+        <v>6</v>
       </c>
       <c r="E131" s="11">
-        <v>20.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="28.5">
       <c r="A132" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="E132" s="11">
-        <v>12.9</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="28.5">
       <c r="A133" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D133" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E133" s="11">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="28.5">
+      <c r="A134" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E133" s="11">
+      <c r="C134" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E134" s="11">
         <v>10.9</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="28.5">
-      <c r="A134" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E134" s="13">
-        <v>12.9</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="28.5">
       <c r="A135" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E135" s="13">
-        <v>12</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="28.5">
       <c r="A136" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E136" s="13">
-        <v>4.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="28.5">
       <c r="A137" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E137" s="13">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="28.5">
+      <c r="A138" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B138" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="E137" s="13">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="E138" s="13">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>217</v>
+        <v>28</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>217</v>
+        <v>28</v>
       </c>
       <c r="E139" s="13">
-        <v>6.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E140" s="13">
-        <v>14.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="E141" s="13">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="28.5">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>28</v>
@@ -4053,80 +4062,80 @@
         <v>28</v>
       </c>
       <c r="E142" s="13">
-        <v>11.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5">
       <c r="A143" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="E143" s="13">
         <v>11.5</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" ht="28.5">
       <c r="A144" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E144" s="13">
-        <v>5.0999999999999996</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E145" s="13">
-        <v>2</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E146" s="13">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="28.5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>228</v>
@@ -4138,131 +4147,131 @@
         <v>228</v>
       </c>
       <c r="E147" s="13">
-        <v>27.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="28.5">
       <c r="A148" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>43</v>
+        <v>228</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D148" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E148" s="13">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="28.5">
+      <c r="A149" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E148" s="13">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D149" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E149" s="13">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="E149" s="13">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="28.5">
-      <c r="A150" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D150" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E150" s="13">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="28.5">
+      <c r="A151" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="E150" s="13">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E151" s="13">
-        <v>25.9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D152" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E152" s="13">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="E152" s="13">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="28.5">
-      <c r="A153" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D153" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E153" s="13">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="28.5">
+      <c r="A154" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E153" s="13">
+      <c r="C154" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E154" s="13">
         <v>11.5</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="28.5">
-      <c r="A154" s="14" t="s">
+    <row r="155" spans="1:5" ht="28.5">
+      <c r="A155" s="14" t="s">
         <v>239</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E154" s="15">
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="14" t="s">
-        <v>240</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>69</v>
@@ -4274,12 +4283,12 @@
         <v>62</v>
       </c>
       <c r="E155" s="15">
-        <v>16.7</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>69</v>
@@ -4294,9 +4303,9 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="28.5">
+    <row r="157" spans="1:5">
       <c r="A157" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>69</v>
@@ -4313,10 +4322,10 @@
     </row>
     <row r="158" spans="1:5" ht="28.5">
       <c r="A158" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>61</v>
@@ -4325,15 +4334,15 @@
         <v>62</v>
       </c>
       <c r="E158" s="15">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="28.5">
       <c r="A159" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>61</v>
@@ -4342,15 +4351,15 @@
         <v>62</v>
       </c>
       <c r="E159" s="15">
-        <v>17.899999999999999</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" ht="28.5">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>61</v>
@@ -4359,15 +4368,15 @@
         <v>62</v>
       </c>
       <c r="E160" s="15">
-        <v>34.9</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="28.5">
       <c r="A161" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>28</v>
+        <v>247</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>61</v>
@@ -4376,49 +4385,49 @@
         <v>62</v>
       </c>
       <c r="E161" s="15">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="28.5">
       <c r="A162" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>250</v>
+        <v>28</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>250</v>
+        <v>62</v>
       </c>
       <c r="E162" s="15">
-        <v>24.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>69</v>
+        <v>250</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="E163" s="15">
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="28.5">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>61</v>
@@ -4427,15 +4436,15 @@
         <v>62</v>
       </c>
       <c r="E164" s="15">
-        <v>24.9</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="28.5">
       <c r="A165" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>61</v>
@@ -4444,49 +4453,49 @@
         <v>62</v>
       </c>
       <c r="E165" s="15">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="28.5">
       <c r="A166" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="E166" s="15">
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="28.5">
+    <row r="167" spans="1:5">
       <c r="A167" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>69</v>
+        <v>256</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>62</v>
+        <v>256</v>
       </c>
       <c r="E167" s="15">
-        <v>16.5</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="28.5">
       <c r="A168" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>61</v>
@@ -4495,12 +4504,12 @@
         <v>62</v>
       </c>
       <c r="E168" s="15">
-        <v>24.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="28.5">
       <c r="A169" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>66</v>
@@ -4512,15 +4521,15 @@
         <v>62</v>
       </c>
       <c r="E169" s="15">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="28.5">
       <c r="A170" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>61</v>
@@ -4529,49 +4538,49 @@
         <v>62</v>
       </c>
       <c r="E170" s="15">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" ht="28.5">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D171" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E171" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="28.5">
+      <c r="A172" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B172" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="E171" s="15">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="E172" s="15">
-        <v>2.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>61</v>
@@ -4580,182 +4589,182 @@
         <v>62</v>
       </c>
       <c r="E173" s="15">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E174" s="15">
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="16" t="s">
+    <row r="175" spans="1:5">
+      <c r="A175" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B175" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E174" s="17">
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" ht="28.5">
-      <c r="A175" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>267</v>
+        <v>91</v>
       </c>
       <c r="E175" s="17">
-        <v>13.5</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="28.5">
       <c r="A176" s="16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="E176" s="17">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="28.5">
       <c r="A177" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C177" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D177" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E177" s="17">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="28.5">
+      <c r="A178" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="E177" s="17">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D178" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E178" s="17">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="E178" s="17">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="28.5">
-      <c r="A179" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D179" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E179" s="17">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="28.5">
+      <c r="A180" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B180" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="E179" s="17">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D180" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E180" s="17">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="E180" s="17">
-        <v>29.9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="28.5">
-      <c r="A181" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D181" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E181" s="17">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="28.5">
+      <c r="A182" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="E181" s="17">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E182" s="17">
-        <v>16.899999999999999</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E183" s="17">
-        <v>28.1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="28.5">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>84</v>
@@ -4767,63 +4776,63 @@
         <v>84</v>
       </c>
       <c r="E184" s="17">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="28.5">
       <c r="A185" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E185" s="17">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E186" s="17">
-        <v>28.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>267</v>
+        <v>84</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>267</v>
+        <v>84</v>
       </c>
       <c r="E187" s="17">
-        <v>4.9000000000000004</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>267</v>
@@ -4835,63 +4844,63 @@
         <v>267</v>
       </c>
       <c r="E188" s="17">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E189" s="17">
         <v>20.9</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="28.5">
-      <c r="A189" s="18" t="s">
+    <row r="190" spans="1:5" ht="28.5">
+      <c r="A190" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B190" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="C189" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D189" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="E189" s="19">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>152</v>
+        <v>282</v>
       </c>
       <c r="E190" s="19">
-        <v>20.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="E191" s="19">
-        <v>22.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>111</v>
@@ -4903,46 +4912,46 @@
         <v>111</v>
       </c>
       <c r="E192" s="19">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="E193" s="19">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E194" s="19">
-        <v>20.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>148</v>
@@ -4954,29 +4963,29 @@
         <v>148</v>
       </c>
       <c r="E195" s="19">
-        <v>17.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E196" s="19">
-        <v>40.9</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>152</v>
@@ -4988,29 +4997,29 @@
         <v>152</v>
       </c>
       <c r="E197" s="19">
-        <v>4.49</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="E198" s="19">
-        <v>21.9</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>282</v>
@@ -5022,29 +5031,29 @@
         <v>282</v>
       </c>
       <c r="E199" s="19">
-        <v>42</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>98</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E200" s="19">
-        <v>4.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>294</v>
@@ -5056,12 +5065,12 @@
         <v>294</v>
       </c>
       <c r="E201" s="19">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>294</v>
@@ -5073,23 +5082,40 @@
         <v>294</v>
       </c>
       <c r="E202" s="19">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E203" s="19">
         <v>3.2</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
-      <c r="A203" s="20" t="s">
+    <row r="204" spans="1:5">
+      <c r="A204" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="B203" s="21" t="s">
+      <c r="B204" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C203" s="21" t="s">
+      <c r="C204" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="D203" s="21" t="s">
+      <c r="D204" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="E203" s="22">
+      <c r="E204" s="22">
         <v>4.5</v>
       </c>
     </row>
